--- a/outputs/per-fund/vc-investments-haun-ventures.xlsx
+++ b/outputs/per-fund/vc-investments-haun-ventures.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Haun Ventures. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Haun Ventures. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -7011,11 +7011,11 @@
         <v>1</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, haun-ventures</t>
+          <t>1kx, coinbase-ventures, haun-ventures</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -7131,11 +7131,11 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, haun-ventures</t>
+          <t>coinbase-ventures, haun-ventures, jump-crypto</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -7194,11 +7194,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, haun-ventures</t>
+          <t>coinbase-ventures, haun-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -7257,11 +7257,11 @@
         <v>1</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, paradigm, robot-ventures</t>
+          <t>circle-ventures, haun-ventures, paradigm, polygon-ventures, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -7320,11 +7320,11 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, maven11, robot-ventures</t>
+          <t>1kx, haun-ventures, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -7869,11 +7869,11 @@
         <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures</t>
+          <t>galaxy-digital, haun-ventures</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -8058,11 +8058,11 @@
         <v>1</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures</t>
+          <t>galaxy-digital, haun-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -8117,11 +8117,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures</t>
+          <t>haun-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -8422,11 +8422,11 @@
         <v>4</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures</t>
+          <t>galaxy-digital, haun-ventures</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -8544,11 +8544,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, haun-ventures</t>
+          <t>electric-capital, haun-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -8607,11 +8607,11 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures</t>
+          <t>gsr, haun-ventures</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -9026,11 +9026,11 @@
         <v>2</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, haun-ventures</t>
+          <t>bain-capital-crypto, galaxy-digital, haun-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -9215,11 +9215,11 @@
         <v>1</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, haun-ventures</t>
+          <t>coinbase-ventures, haun-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -9343,11 +9343,11 @@
         <v>1</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, haun-ventures</t>
+          <t>coinbase-ventures, coinfund, haun-ventures</t>
         </is>
       </c>
       <c r="M41" s="10" t="n"/>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -11581,13 +11581,13 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Unieke uitgaande domeinen als benadering van portefeuillenamen.</t>
+          <t>Unique outbound domains as an approximation of portfolio names.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
